--- a/src/test/resources/testData/CreateEventHubTestDataScenarios.xlsx
+++ b/src/test/resources/testData/CreateEventHubTestDataScenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\RestAssuredEnterPriseFramework\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5CA232-7628-45F2-9DCD-19316B5CE03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE89A4A4-F153-4C35-828F-B9B7F505C7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1D42A279-7A7A-460B-BC73-D0AAE23E8CA4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="50">
   <si>
     <t>Title</t>
   </si>
@@ -78,60 +78,12 @@
     <t>East Quincy</t>
   </si>
   <si>
-    <t>2026-06-11T14:19:17.689Z</t>
-  </si>
-  <si>
     <t>https://www.joshua-mohr.biz:55235/sint/enimquidem#natus</t>
   </si>
   <si>
-    <t>Beneath the Velvet Tide</t>
-  </si>
-  <si>
-    <t>Adipisci inventore temporibus.</t>
-  </si>
-  <si>
-    <t>fjmroplqza</t>
-  </si>
-  <si>
-    <t>1842 Cedar Hollow</t>
-  </si>
-  <si>
-    <t>Northvale</t>
-  </si>
-  <si>
-    <t>2026-06-12T09:42:11.214Z</t>
-  </si>
-  <si>
-    <t>https://www.elliot-bins.org:44121/voluptas/illum#amet</t>
-  </si>
-  <si>
-    <t>Echoes of Amber Light</t>
-  </si>
-  <si>
-    <t>Doloremque est recusandae.</t>
-  </si>
-  <si>
-    <t>nvkxqtrmpe</t>
-  </si>
-  <si>
-    <t>9057 Maple Crest</t>
-  </si>
-  <si>
-    <t>Springbrook</t>
-  </si>
-  <si>
-    <t>2026-06-13T16:08:44.903Z</t>
-  </si>
-  <si>
-    <t>https://www.kian-hilpert.net:50877/ipsum/dolor#sint</t>
-  </si>
-  <si>
     <t>The Silent Orchard</t>
   </si>
   <si>
-    <t>Corporis esse minima.</t>
-  </si>
-  <si>
     <t>hqzvmlnser</t>
   </si>
   <si>
@@ -147,9 +99,6 @@
     <t>https://www.haley-berge.com:63210/quaerat/soluta#dolor</t>
   </si>
   <si>
-    <t>Ashes Beneath Horizon</t>
-  </si>
-  <si>
     <t>Mollitia consequuntur aut.</t>
   </si>
   <si>
@@ -186,46 +135,55 @@
     <t>ExpectedErrorMessage</t>
   </si>
   <si>
-    <t>CreateAirline_DuplicateID</t>
-  </si>
-  <si>
-    <t>Create airline with existing airline ID</t>
-  </si>
-  <si>
-    <t>there is an airline registered under same id you've entered</t>
-  </si>
-  <si>
-    <t>CreateAirline_EmptyPayload</t>
-  </si>
-  <si>
-    <t>Create arline with empty payload</t>
-  </si>
-  <si>
-    <t>valid airline data must submit.</t>
-  </si>
-  <si>
-    <t>CreateAirline_OnlyID</t>
-  </si>
-  <si>
-    <t>Create airline with just ID</t>
-  </si>
-  <si>
-    <t>error in saving data</t>
-  </si>
-  <si>
-    <t>CreateAirline_WithoutID</t>
-  </si>
-  <si>
-    <t>Create airline without ID</t>
-  </si>
-  <si>
     <t>NO_DATA</t>
   </si>
   <si>
-    <t>CreateAirline_HappyPath</t>
-  </si>
-  <si>
-    <t>Create airline with expected request payload</t>
+    <t>CreateEvent_WithoutTitle</t>
+  </si>
+  <si>
+    <t>Create Event without title</t>
+  </si>
+  <si>
+    <t>Title is required</t>
+  </si>
+  <si>
+    <t>CreateEvent_InvalidDate</t>
+  </si>
+  <si>
+    <t>Internal server error</t>
+  </si>
+  <si>
+    <t>Create Event with invalid date</t>
+  </si>
+  <si>
+    <t>CreateEvent_EmptyPayload</t>
+  </si>
+  <si>
+    <t>Create Event with empty payload</t>
+  </si>
+  <si>
+    <t>Validation failed</t>
+  </si>
+  <si>
+    <t>CreateEvent_HappyPath</t>
+  </si>
+  <si>
+    <t>Event created successfully</t>
+  </si>
+  <si>
+    <t>Holi Celebration</t>
+  </si>
+  <si>
+    <t>CreateEvent_WithoutDescription</t>
+  </si>
+  <si>
+    <t>Create a succesful Event</t>
+  </si>
+  <si>
+    <t>Create event without description</t>
+  </si>
+  <si>
+    <t>2026-06-15T</t>
   </si>
 </sst>
 </file>
@@ -321,7 +279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -336,10 +294,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -658,10 +614,10 @@
   <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="46.85546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="46.85546875" customWidth="1"/>
     <col min="5" max="5" width="34.28515625" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="24.5703125" customWidth="1"/>
@@ -673,17 +629,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>49</v>
+      <c r="A1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
@@ -713,21 +669,21 @@
         <v>8</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>50</v>
+      <c r="A2" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="9">
-        <v>400</v>
+        <v>39</v>
+      </c>
+      <c r="C2" s="1">
+        <v>500</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -744,8 +700,8 @@
       <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
+      <c r="J2" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="K2" s="1">
         <v>150</v>
@@ -754,130 +710,130 @@
         <v>425</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="33" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>53</v>
+      <c r="A3" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="9">
+        <v>41</v>
+      </c>
+      <c r="C3" s="1">
         <v>400</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="4">
-        <v>299</v>
-      </c>
-      <c r="L3" s="4">
-        <v>180</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>56</v>
+      <c r="A4" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="9">
+        <v>35</v>
+      </c>
+      <c r="C4" s="1">
         <v>400</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="K4" s="4">
+        <v>1200</v>
+      </c>
+      <c r="L4" s="4">
+        <v>340</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="4">
-        <v>520</v>
-      </c>
-      <c r="L4" s="4">
-        <v>250</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>45</v>
-      </c>
     </row>
-    <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>59</v>
+    <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="9">
-        <v>200</v>
+        <v>48</v>
+      </c>
+      <c r="C5" s="1">
+        <v>201</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K5" s="4">
         <v>875</v>
@@ -886,42 +842,42 @@
         <v>95</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="33" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>62</v>
+      <c r="A6" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="9">
-        <v>200</v>
+        <v>47</v>
+      </c>
+      <c r="C6" s="1">
+        <v>201</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K6" s="4">
         <v>1200</v>
@@ -930,21 +886,20 @@
         <v>340</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1" location="natus" xr:uid="{204BAC1A-38D7-44E2-AACB-D46DCF370869}"/>
     <hyperlink ref="M6" r:id="rId2" location="eum" xr:uid="{D9F272E9-B975-43E4-9B67-A5F57A2333D8}"/>
-    <hyperlink ref="M3" r:id="rId3" location="amet" xr:uid="{6F3F5990-CC37-43B0-80A2-D6138DB30D28}"/>
-    <hyperlink ref="M4" r:id="rId4" location="sint" xr:uid="{287FFB5D-15DB-4D81-B0D2-DF8B4E70B4DE}"/>
-    <hyperlink ref="M5" r:id="rId5" location="dolor" xr:uid="{DC7A98FD-3E7B-470A-9B29-C4F88F0C3A43}"/>
+    <hyperlink ref="M5" r:id="rId3" location="dolor" xr:uid="{DC7A98FD-3E7B-470A-9B29-C4F88F0C3A43}"/>
+    <hyperlink ref="M4" r:id="rId4" location="eum" xr:uid="{9E58F45F-8291-49E0-B286-85E159656A99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/src/test/resources/testData/CreateEventHubTestDataScenarios.xlsx
+++ b/src/test/resources/testData/CreateEventHubTestDataScenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\RestAssuredEnterPriseFramework\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE89A4A4-F153-4C35-828F-B9B7F505C7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223F907F-083F-43BC-93F3-D544C51431CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1D42A279-7A7A-460B-BC73-D0AAE23E8CA4}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{1D42A279-7A7A-460B-BC73-D0AAE23E8CA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -123,9 +123,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>ScenaroID</t>
-  </si>
-  <si>
     <t>ScenarioDesc</t>
   </si>
   <si>
@@ -184,6 +181,9 @@
   </si>
   <si>
     <t>2026-06-15T</t>
+  </si>
+  <si>
+    <t>ScenarioId</t>
   </si>
 </sst>
 </file>
@@ -630,16 +630,16 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
@@ -674,16 +674,16 @@
     </row>
     <row r="2" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1">
         <v>500</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -701,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K2" s="1">
         <v>150</v>
@@ -718,43 +718,43 @@
     </row>
     <row r="3" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="C3" s="1">
         <v>400</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>28</v>
@@ -762,19 +762,19 @@
     </row>
     <row r="4" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="C4" s="1">
         <v>400</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>21</v>
@@ -806,22 +806,22 @@
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1">
         <v>201</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>16</v>
@@ -850,19 +850,19 @@
     </row>
     <row r="6" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1">
         <v>201</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>21</v>

--- a/src/test/resources/testData/CreateEventHubTestDataScenarios.xlsx
+++ b/src/test/resources/testData/CreateEventHubTestDataScenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\RestAssuredEnterPriseFramework\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223F907F-083F-43BC-93F3-D544C51431CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1498DB08-08F6-4D04-B752-541E608210CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{1D42A279-7A7A-460B-BC73-D0AAE23E8CA4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
   <si>
     <t>Title</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Westbrook</t>
   </si>
   <si>
-    <t>2026-06-14T11:23:59.107Z</t>
-  </si>
-  <si>
     <t>https://www.haley-berge.com:63210/quaerat/soluta#dolor</t>
   </si>
   <si>
@@ -184,6 +181,12 @@
   </si>
   <si>
     <t>ScenarioId</t>
+  </si>
+  <si>
+    <t>2027-06-14T11:23:59.107Z</t>
+  </si>
+  <si>
+    <t>2027-06-15T18:55:03.771Z</t>
   </si>
 </sst>
 </file>
@@ -630,16 +633,16 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
@@ -669,21 +672,21 @@
         <v>8</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1">
         <v>500</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -701,7 +704,7 @@
         <v>13</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K2" s="1">
         <v>150</v>
@@ -713,83 +716,83 @@
         <v>14</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="C3" s="1">
         <v>400</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="C4" s="1">
         <v>400</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="K4" s="4">
         <v>1200</v>
@@ -798,30 +801,30 @@
         <v>340</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1">
         <v>201</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>16</v>
@@ -833,7 +836,7 @@
         <v>18</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="K5" s="4">
         <v>875</v>
@@ -842,42 +845,42 @@
         <v>95</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1">
         <v>201</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="F6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="J6" s="4" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K6" s="4">
         <v>1200</v>
@@ -886,10 +889,10 @@
         <v>340</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testData/CreateEventHubTestDataScenarios.xlsx
+++ b/src/test/resources/testData/CreateEventHubTestDataScenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\RestAssuredEnterPriseFramework\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1498DB08-08F6-4D04-B752-541E608210CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A14E554-0B92-4DD1-8F5B-6FF6A4F8B1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{1D42A279-7A7A-460B-BC73-D0AAE23E8CA4}"/>
+    <workbookView xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11385" xr2:uid="{1D42A279-7A7A-460B-BC73-D0AAE23E8CA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="50">
   <si>
     <t>Title</t>
   </si>
@@ -144,9 +144,6 @@
     <t>CreateEvent_InvalidDate</t>
   </si>
   <si>
-    <t>Internal server error</t>
-  </si>
-  <si>
     <t>Create Event with invalid date</t>
   </si>
   <si>
@@ -177,9 +174,6 @@
     <t>Create event without description</t>
   </si>
   <si>
-    <t>2026-06-15T</t>
-  </si>
-  <si>
     <t>ScenarioId</t>
   </si>
   <si>
@@ -187,6 +181,9 @@
   </si>
   <si>
     <t>2027-06-15T18:55:03.771Z</t>
+  </si>
+  <si>
+    <t>Event date must be a valid ISO 8601 date</t>
   </si>
 </sst>
 </file>
@@ -282,7 +279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -298,7 +295,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -633,7 +629,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>28</v>
@@ -680,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -703,8 +699,8 @@
       <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>47</v>
+      <c r="J2" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K2" s="1">
         <v>150</v>
@@ -721,16 +717,16 @@
     </row>
     <row r="3" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="C3" s="1">
         <v>400</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>31</v>
@@ -809,16 +805,16 @@
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1">
         <v>201</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>15</v>
@@ -836,7 +832,7 @@
         <v>18</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K5" s="4">
         <v>875</v>
@@ -853,19 +849,19 @@
     </row>
     <row r="6" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="1">
         <v>201</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>20</v>
@@ -880,7 +876,7 @@
         <v>23</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K6" s="4">
         <v>1200</v>
